--- a/artfynd/A 38860-2025 artfynd.xlsx
+++ b/artfynd/A 38860-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94683840</v>
+        <v>103178782</v>
       </c>
       <c r="B2" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223609</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vedborm norra, Öl</t>
+          <t>Kalmar län, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620398.1961443848</v>
+        <v>620312</v>
       </c>
       <c r="R2" t="n">
-        <v>6342619.082932888</v>
+        <v>6342582</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,24 +742,19 @@
           <t>Högby</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>700BA10E-3E85-4480-9F30-1780C7CC0A3F</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,34 +763,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Nilsson</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Nilsson, Börje Ekstam</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94684066</v>
+        <v>94683840</v>
       </c>
       <c r="B3" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,27 +796,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>223609</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Epipactis helleborine subsp. helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -840,17 +824,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vedborm norra, Vedborms träsk, Öl</t>
+          <t>Vedborm norra, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620412.5889992218</v>
+        <v>620399</v>
       </c>
       <c r="R3" t="n">
-        <v>6342702.410161805</v>
+        <v>6342619</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,19 +861,9 @@
           <t>2021-07-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,6 +888,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>94684066</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vedborm norra, Vedborms träsk, Öl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>620413</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6342702</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Högby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-07-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-07-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Viktoria Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Viktoria Nilsson, Börje Ekstam</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38860-2025 artfynd.xlsx
+++ b/artfynd/A 38860-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178782</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94683840</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,8 +1009,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94684066</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>